--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260902.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>10,800,000</t>
+          <t>10,500,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>15.59%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>6.49%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.62%</t>
         </is>
       </c>
     </row>
@@ -704,73 +704,73 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.13%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>1,115,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.01%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,115,000</t>
+          <t>810,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.94%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>810,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.92%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
@@ -809,56 +809,56 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>2,087,956</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,880,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>2,750,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -902,73 +902,73 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>189,500</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,640,000</t>
+          <t>13,500,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>2,640,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1056,68 +1056,68 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>149,500</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,050,000</t>
+          <t>1,737,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,737,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,22 +1129,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>850,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1261,44 +1261,44 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>860,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1364,134 +1364,134 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>3,100,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,100,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -1569,78 +1569,78 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1723,35 +1723,39 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>8,461,882,340</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr"/>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7,619,396,271</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1759,17 +1763,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2,668,305,718</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1777,20 +1781,38 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>3,619,104,637</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
           <t>RP_NTD</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>4,176,089,384</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr"/>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>3,426,046,480</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
